--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.752103499999976</v>
+        <v>4.520176999999876</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.729909899999939</v>
+        <v>4.425252399999863</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.428204499999993</v>
+        <v>4.482782300000054</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>5.288753799999995</v>
+        <v>4.50659799999994</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.38410859999999</v>
+        <v>4.603195600000163</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.227943200000027</v>
+        <v>4.591144099999838</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.4 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.4 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.3 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.4 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.2 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.9 초</t>
+          <t>28.2 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.520176999999876</v>
+        <v>4.602012800000011</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.425252399999863</v>
+        <v>4.420665499999814</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.482782300000054</v>
+        <v>4.510886900000514</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.50659799999994</v>
+        <v>4.563906999999745</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.603195600000163</v>
+        <v>4.586269999999786</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.591144099999838</v>
+        <v>4.722951300000204</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28.2 초</t>
+          <t>28.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.602012800000011</v>
+        <v>4.610873000000538</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.420665499999814</v>
+        <v>4.452440799999749</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.510886900000514</v>
+        <v>4.546999099999994</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.563906999999745</v>
+        <v>4.655793199999607</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.586269999999786</v>
+        <v>4.693758800000069</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.722951300000204</v>
+        <v>4.643061400000079</v>
       </c>
     </row>
   </sheetData>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.4 초</t>
+          <t>4.5 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28.4 초</t>
+          <t>28.6 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.610873000000538</v>
+        <v>4.659275199999684</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.452440799999749</v>
+        <v>4.459832299999107</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.546999099999994</v>
+        <v>4.530006400000275</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.655793199999607</v>
+        <v>4.579381400000784</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.693758800000069</v>
+        <v>4.572922499999549</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.643061400000079</v>
+        <v>4.672549799999615</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>4.6 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28.6 초</t>
+          <t>28.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.659275199999684</v>
+        <v>8.528859500000181</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.459832299999107</v>
+        <v>8.387422900001184</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.530006400000275</v>
+        <v>5.003034999999727</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.579381400000784</v>
+        <v>8.772573599999305</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.572922499999549</v>
+        <v>9.392486999999164</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.672549799999615</v>
+        <v>6.094110100000762</v>
       </c>
     </row>
   </sheetData>
@@ -5712,7 +5712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5822,83 +5822,81 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.3 경제성DR</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8264580.235272408</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>목표 5,180 kW (기준 5,293.4 → 실제 5,180.0) · 150 kW / 100 kWh · 회수 31.7년</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>거래 가능일 245일 · 등록 권장 2,011 kW · 연간 감축 34,350 kWh</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>C2 오후 피크형</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7.1 선택요금 전환</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>53336990.5199995</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>53336990.5199995</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>I → II</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7.2 계약전력 조정</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>계약 5,823 kW 가정 (관측 최대 × 1.1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.4 역률 개선 (92→97%)</t>
+          <t>7.2 계약전력 조정</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4528326.239999771</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4528326.239999771</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>높음</t>
@@ -5906,136 +5904,133 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>요금표와 약관만으로 확정</t>
+          <t>계약 5,823 kW 가정 (관측 최대 × 1.1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.3 경제성DR</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4528326.239999771</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4528326.239999771</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 1,758 kW · 연간 감축 28,632 kWh</t>
+          <t>요금표와 약관만으로 확정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C3 평탄형</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.1 선택요금 전환</t>
+          <t>7.6 ESS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84638858.3569994</v>
-      </c>
-      <c r="D10" t="n">
-        <v>84638858.3569994</v>
-      </c>
+        <v>8267937.323272228</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간~낮음</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>I → III</t>
+          <t>목표 5,180 kW (기준 5,293.4 → 실제 5,180.0) · 150 kW / 100 kWh · 회수 31.7년</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.2 계약전력 조정</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>거래 가능일 245일 · 등록 권장 1,758 kW · 연간 감축 28,632 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C3 평탄형</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>84638858.3569994</v>
+      </c>
+      <c r="D12" t="n">
+        <v>84638858.3569994</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>계약 3,358 kW 가정 (관측 최대 × 1.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7.4 역률 개선 (92→97%)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2634668.25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2634668.25</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>요금표와 약관만으로 확정</t>
+          <t>I → III</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.3 경제성DR</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 13 kW · 연간 감축 72,603 kWh</t>
+          <t>계약 3,358 kW 가정 (관측 최대 × 1.1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>C4 주말 가동형</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.1 선택요금 전환</t>
+          <t>7.4 역률 개선 (92→97%)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>62101674.57999992</v>
+        <v>2634668.25</v>
       </c>
       <c r="D14" t="n">
-        <v>62101674.57999992</v>
+        <v>2634668.25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6044,90 +6039,86 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>I → II</t>
+          <t>요금표와 약관만으로 확정</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2 계약전력 조정</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간~낮음</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>계약 5,823 kW 가정 (관측 최대 × 1.1)</t>
+          <t>최소 규격 미달 — 필요 출력 17.3 kW &lt; 상업용 최소 50 kW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>7.4 역률 개선 (92→97%)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4528326.239999771</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4528326.239999771</v>
-      </c>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>거래 가능일 245일 · 등록 권장 13 kW · 연간 감축 72,603 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C4 주말 가동형</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>62101674.57999992</v>
+      </c>
+      <c r="D17" t="n">
+        <v>62101674.57999992</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>요금표와 약관만으로 확정</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7.3 경제성DR</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 849 kW · 연간 감축 222,052 kWh</t>
+          <t>I → II</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>C5 겨울 피크형</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.1 선택요금 전환</t>
+          <t>7.2 계약전력 조정</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48131301.02000046</v>
-      </c>
-      <c r="D18" t="n">
-        <v>48131301.02000046</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>높음</t>
@@ -6135,20 +6126,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>I → II</t>
+          <t>계약 5,823 kW 가정 (관측 최대 × 1.1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>7.2 계약전력 조정</t>
+          <t>7.4 역률 개선 (92→97%)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>4528326.239999771</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4528326.239999771</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>높음</t>
@@ -6156,30 +6149,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>계약 6,792 kW 가정 (관측 최대 × 1.1)</t>
+          <t>요금표와 약관만으로 확정</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.4 역률 개선 (92→97%)</t>
+          <t>7.6 ESS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4419725.888000488</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4419725.888000488</v>
-      </c>
+        <v>8261895.513091087</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간~낮음</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>요금표와 약관만으로 확정</t>
+          <t>목표 5,180 kW (기준 5,293.4 → 실제 5,180.0) · 150 kW / 100 kWh · 회수 31.7년</t>
         </is>
       </c>
     </row>
@@ -6198,14 +6189,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 1,714 kW · 연간 감축 29,004 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 849 kW · 연간 감축 222,052 kWh</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C6 야간 피크형</t>
+          <t>C5 겨울 피크형</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6214,10 +6205,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>86064273.07500029</v>
+        <v>48131301.02000046</v>
       </c>
       <c r="D22" t="n">
-        <v>86064273.07500029</v>
+        <v>48131301.02000046</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -6237,7 +6228,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>69555562.36799997</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
@@ -6247,7 +6238,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>계약 12,013 kW 가정 (관측 최대 × 1.1)</t>
+          <t>계약 6,792 kW 가정 (관측 최대 × 1.1)</t>
         </is>
       </c>
     </row>
@@ -6258,10 +6249,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2395867.111000061</v>
+        <v>4419725.888000488</v>
       </c>
       <c r="D24" t="n">
-        <v>2395867.111000061</v>
+        <v>4419725.888000488</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -6277,17 +6268,148 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.3 경제성DR</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6163143.925454617</v>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>목표 5,970 kW (기준 6,174.7 → 실제 5,970.0) · 250 kW / 200 kWh · 회수 56.1년</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>거래 가능일 245일 · 등록 권장 1,714 kW · 연간 감축 29,004 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>86064273.07500029</v>
+      </c>
+      <c r="D27" t="n">
+        <v>86064273.07500029</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>I → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>69555562.36799997</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>계약 12,013 kW 가정 (관측 최대 × 1.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2395867.111000061</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2395867.111000061</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>요금표와 약관만으로 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>성립하는 목표 없음 — 참고 지점 5개 중 절감액 0 이하 5개</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>거래 가능일 245일 · 등록 권장 1,126 kW · 연간 감축 19,442 kWh</t>
         </is>
@@ -6295,12 +6417,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6312,7 +6434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6513,14 +6635,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C2 오후 피크형</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PV 0 kWp 절감액이 정확히 0</t>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6530,14 +6647,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.000000 원</t>
+          <t>viable=True · 목표 5,180 kW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6547,14 +6664,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0 → 78,577,462 → 157,154,857 → 314,299,480</t>
+          <t>목표 5,180 kW · 절감액 8,264,580 원</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기본요금 절감액 단조 증가 후 포화</t>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6564,14 +6681,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>증분 1,250,215 → 0 → 0</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>용량 증가 시 요금적용전력 단조 감소</t>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6581,14 +6698,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5,293.4 → 5,287.7 → 5,287.7 → 5,287.7</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C2 오후 피크형</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6598,14 +6720,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>최대 편차 0.010%</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기준값이 범위 안에 있음</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6615,14 +6737,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>벗어난 지표 0건</t>
+          <t>0 → 78,577,462 → 157,154,857 → 314,299,480</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6632,14 +6754,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>기본요금 절감액 상한: 평탄형</t>
+          <t>증분 1,250,215 → 0 → 0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6649,14 +6771,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53,336,991 원 · I → II</t>
+          <t>5,293.4 → 5,287.7 → 5,287.7 → 5,287.7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6666,14 +6788,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4,528,326 원 (기본요금 452,832,624 의 1.00%)</t>
+          <t>최대 편차 0.010%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+          <t>기준값이 범위 안에 있음</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6683,19 +6805,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>245 / 359일</t>
+          <t>벗어난 지표 0건</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C3 평탄형</t>
-        </is>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PV 0 kWp 절감액이 정확히 0</t>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6705,14 +6822,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.000000 원</t>
+          <t>기본요금 절감액 상한: 평탄형</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6722,14 +6839,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0 → 78,883,247 → 157,766,493 → 315,532,987</t>
+          <t>53,336,991 원 · I → II</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>기본요금 절감액 단조 증가 후 포화</t>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6739,14 +6856,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>증분 4,260,002 → 1,654,689 → 2,638,617</t>
+          <t>4,528,326 원 (기본요금 452,832,624 의 1.00%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>용량 증가 시 요금적용전력 단조 감소</t>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6756,14 +6873,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3,052.3 → 3,032.1 → 3,026.2 → 3,014.2</t>
+          <t>245 / 359일</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6773,14 +6890,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>최대 편차 0.017%</t>
+          <t>viable=True · 목표 5,180 kW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>기준값이 범위 안에 있음</t>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6790,14 +6907,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>벗어난 지표 0건</t>
+          <t>목표 5,180 kW · 절감액 8,267,937 원</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6807,14 +6924,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>기본요금 절감액 상한: 평탄형</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6824,14 +6941,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>84,638,858 원 · I → III</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C3 평탄형</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6841,14 +6963,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2,634,668 원 (기본요금 263,466,825 의 1.00%)</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6858,19 +6980,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>245 / 359일</t>
+          <t>0 → 78,883,247 → 157,766,493 → 315,532,987</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>C4 주말 가동형</t>
-        </is>
-      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PV 0 kWp 절감액이 정확히 0</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6880,14 +6997,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.000000 원</t>
+          <t>증분 4,260,002 → 1,654,689 → 2,638,617</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6897,14 +7014,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0 → 89,087,627 → 178,175,254 → 356,350,508</t>
+          <t>3,052.3 → 3,032.1 → 3,026.2 → 3,014.2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>기본요금 절감액 단조 증가 후 포화</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6914,14 +7031,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>증분 12,701,894 → 5,257,957 → 3,897,197</t>
+          <t>최대 편차 0.017%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>용량 증가 시 요금적용전력 단조 감소</t>
+          <t>기준값이 범위 안에 있음</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6931,14 +7048,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5,293.4 → 5,204.0 → 5,198.0 → 5,186.1</t>
+          <t>벗어난 지표 0건</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6948,14 +7065,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>최대 편차 0.017%</t>
+          <t>기본요금 절감액 상한: 평탄형</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>기준값이 범위 안에 있음</t>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6965,14 +7082,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>벗어난 지표 0건</t>
+          <t>84,638,858 원 · I → III</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6982,14 +7099,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>기본요금 절감액 상한: 기준, 평탄형</t>
+          <t>2,634,668 원 (기본요금 263,466,825 의 1.00%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6999,14 +7116,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>62,101,675 원 · I → II</t>
+          <t>245 / 359일</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7016,14 +7133,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4,528,326 원 (기본요금 452,832,624 의 1.00%)</t>
+          <t>viable=False · 목표 0 kW</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7033,19 +7150,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>245 / 359일</t>
+          <t>목표 0 kW · 절감액 —</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>C5 겨울 피크형</t>
-        </is>
-      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PV 0 kWp 절감액이 정확히 0</t>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7055,14 +7167,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.000000 원</t>
+          <t>어긋난 점 0개 / 0개</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7072,14 +7184,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0 → 78,883,247 → 157,766,493 → 315,528,356</t>
+          <t>어긋난 점 0개 / 0개</t>
         </is>
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C4 주말 가동형</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기본요금 절감액 단조 증가 후 포화</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7089,14 +7206,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>증분 4,562,906 → 1,909,551 → 3,180,364</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>용량 증가 시 요금적용전력 단조 감소</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7106,14 +7223,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6,174.7 → 6,166.0 → 6,157.2 → 6,139.8</t>
+          <t>0 → 89,087,627 → 178,175,254 → 356,350,508</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7123,14 +7240,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>최대 편차 0.017%</t>
+          <t>증분 12,701,894 → 5,257,957 → 3,897,197</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>기준값이 범위 안에 있음</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7140,14 +7257,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>벗어난 지표 0건</t>
+          <t>5,293.4 → 5,204.0 → 5,198.0 → 5,186.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7157,14 +7274,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>기본요금 절감액 상한: 평탄형</t>
+          <t>최대 편차 0.017%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+          <t>기준값이 범위 안에 있음</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7174,14 +7291,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>48,131,301 원 · I → II</t>
+          <t>벗어난 지표 0건</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7191,14 +7308,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4,419,726 원 (기본요금 441,972,589 의 1.00%)</t>
+          <t>기본요금 절감액 상한: 기준, 평탄형</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7208,19 +7325,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>245 / 359일</t>
+          <t>62,101,675 원 · I → II</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C6 야간 피크형</t>
-        </is>
-      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PV 0 kWp 절감액이 정확히 0</t>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7230,14 +7342,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.000000 원</t>
+          <t>4,528,326 원 (기본요금 452,832,624 의 1.00%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7247,14 +7359,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0 → 78,883,247 → 157,756,973 → 308,458,353</t>
+          <t>245 / 359일</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>기본요금 절감액 단조 증가 후 포화</t>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7264,14 +7376,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>증분 9,198,979 → 2,039,809 → 3,427,576</t>
+          <t>viable=True · 목표 5,180 kW</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>용량 증가 시 요금적용전력 단조 감소</t>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7281,14 +7393,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2,801.0 → 2,732.3 → 2,715.5 → 2,701.9</t>
+          <t>목표 5,180 kW · 절감액 8,261,896 원</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7298,14 +7410,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>최대 편차 0.017%</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>기준값이 범위 안에 있음</t>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7315,14 +7427,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>벗어난 지표 0건</t>
+          <t>어긋난 점 0개 / 21개</t>
         </is>
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C5 겨울 피크형</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7332,14 +7449,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>기본요금 절감액 상한: 평탄형</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7349,14 +7466,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>86,064,273 원 · I → II</t>
+          <t>0 → 78,883,247 → 157,766,493 → 315,528,356</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7366,14 +7483,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2,395,867 원 (기본요금 239,586,711 의 1.00%)</t>
+          <t>증분 4,562,906 → 1,909,551 → 3,180,364</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7383,19 +7500,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>245 / 359일</t>
+          <t>6,174.7 → 6,166.0 → 6,157.2 → 6,139.8</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>교차</t>
-        </is>
-      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7405,14 +7517,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C1 95.4 kW vs C2 5.8 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+          <t>최대 편차 0.017%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+          <t>기준값이 범위 안에 있음</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7422,14 +7534,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.1 kW)</t>
+          <t>벗어난 지표 0건</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7439,14 +7551,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>저감률 C5 0.28% vs C1 1.80% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+          <t>기본요금 절감액 상한: 평탄형</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7456,14 +7568,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>관측 10,920.6 kW vs 요금적용 2,801.0 kW (74.4% 낮다)</t>
+          <t>48,131,301 원 · I → II</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>C6 야간 피크형의 PV 기여가 오히려 크다 (저감률)</t>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7473,22 +7585,440 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>저감률 C6 3.05% vs C1 1.80% — 대상 슬롯이 주간뿐이라 PV 가 그대로 듣는다</t>
+          <t>4,419,726 원 (기본요금 441,972,589 의 1.00%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>245 / 359일</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>viable=True · 목표 5,970 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>목표 5,970 kW · 절감액 6,163,144 원</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 25개</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 25개</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0.000000 원</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0 → 78,883,247 → 157,756,973 → 308,458,353</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>증분 9,198,979 → 2,039,809 → 3,427,576</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2,801.0 → 2,732.3 → 2,715.5 → 2,701.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>최대 편차 0.017%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>기준값이 범위 안에 있음</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>벗어난 지표 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 상한: 평탄형</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>86,064,273 원 · I → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2,395,867 원 (기본요금 239,586,711 의 1.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>245 / 359일</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>viable=False · 목표 0 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>목표 0 kW · 절감액 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 5개</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 5개</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>교차</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C1 95.4 kW vs C2 5.8 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.1 kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>저감률 C5 0.28% vs C1 1.80% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>관측 10,920.6 kW vs 요금적용 2,801.0 kW (74.4% 낮다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형의 PV 기여가 오히려 크다 (저감률)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>저감률 C6 3.05% vs C1 1.80% — 대상 슬롯이 주간뿐이라 PV 가 그대로 듣는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
           <t>C4 산업용(을) 주말 할인이 PV 최성기와 겹쳐 전력량요금 절감 비율이 낮다</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>C4 4.95% vs C1 5.44% (봄·가을 토·일·공휴일 11~14시 할인 구간의 단가가 이미 낮다)</t>
         </is>
@@ -7496,13 +8026,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="A52:A61"/>
-    <mergeCell ref="A42:A51"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="A72:A85"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A58:A71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7537,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>8.5 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>5.0 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>8.8 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>9.4 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>6.1 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28.5 초</t>
+          <t>47.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.528859500000181</v>
+        <v>8.115383700001985</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.387422900001184</v>
+        <v>7.975944400001026</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.003034999999727</v>
+        <v>4.709814999998343</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.772573599999305</v>
+        <v>8.239192500001081</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.392486999999164</v>
+        <v>8.856030399998417</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.094110100000762</v>
+        <v>5.67596340000091</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>8.0 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.0 초</t>
+          <t>4.7 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>8.9 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>5.7 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>47.3 초</t>
+          <t>44.6 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.115383700001985</v>
+        <v>8.11282090000168</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7.975944400001026</v>
+        <v>7.968095599997469</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.709814999998343</v>
+        <v>4.705198399999063</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.239192500001081</v>
+        <v>8.230583799999295</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8.856030399998417</v>
+        <v>9.020295199999964</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.67596340000091</v>
+        <v>5.787419500000397</v>
       </c>
     </row>
   </sheetData>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>9.0 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.7 초</t>
+          <t>5.8 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>44.6 초</t>
+          <t>44.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260825.xlsx
+++ b/output/casestudy_20260825.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.11282090000168</v>
+        <v>21.13026040000841</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7.968095599997469</v>
+        <v>19.67607709998265</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.705198399999063</v>
+        <v>12.38487469998654</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.230583799999295</v>
+        <v>20.83812650002073</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.020295199999964</v>
+        <v>23.12321320001502</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.787419500000397</v>
+        <v>15.24486330000218</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>21.1 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.0 초</t>
+          <t>19.7 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>12.4 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>20.8 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.0 초</t>
+          <t>23.1 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.8 초</t>
+          <t>15.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>44.9 초</t>
+          <t>114.7 초</t>
         </is>
       </c>
     </row>
